--- a/output/quickfixclose8_portfolio_daily.xlsx
+++ b/output/quickfixclose8_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>186,158.24</t>
+          <t>184,197.99</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+86.16%</t>
+          <t>+84.20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>192,457  (+92.46%)</t>
+          <t>190,649  (+90.65%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,686  (6.3 pts of return)</t>
+          <t>3,896  (6.5 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.7x</t>
+          <t>4.6x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,262  (-1.29%)</t>
+          <t>-1,276  (-1.28%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5715,22 +5715,70 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>186158.24</v>
+        <v>186329.03</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>7107.69</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>179221.34</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>186329.03</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>7107.69</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>179221.34</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>184197.99</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>186158.24</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>184197.99</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-2,030); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9927,7 @@
         <v>-35.12</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>217061.38</v>
+        <v>213958.15</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9903,14 +9951,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>199333.86</v>
@@ -9919,14 +9975,14 @@
         <v>2770.74</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>-110.83</v>
+        <v>-3214.06</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>217096.5</v>
+        <v>213993.27</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose8_portfolio_daily.xlsx
+++ b/output/quickfixclose8_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>184,197.99</t>
+          <t>218,367.58</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+84.20%</t>
+          <t>+118.37%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>190,649  (+90.65%)</t>
+          <t>226,032  (+126.03%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,896  (6.5 pts of return)</t>
+          <t>3,985  (7.7 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.6x</t>
+          <t>6.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.0 bars</t>
+          <t>4.1 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+7.10R  (best +27.82R)</t>
+          <t>+7.30R  (best +27.82R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,080  (+7.10%)</t>
+          <t>7,911  (+7.30%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5763,22 +5763,86 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>184197.99</v>
+        <v>184298.77</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>-0</v>
+        <v>5357.46</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>184197.99</v>
+        <v>178941.3</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-2,030); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>218399.98</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>7082.64</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>211317.34</v>
+      </c>
+      <c r="E189" t="n">
+        <v>4</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 1,789); Nasdaq_100_E_mini short (risk 1,772); S_P_500_E_mini short (risk 1,754)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+21,646); Corn_CBOT_Futures exit_close (+12,456)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>218367.58</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>218367.58</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,113)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9822,14 +9886,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>12.038</v>
       </c>
       <c r="G79" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.019</v>
+        <v>12</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>207882.63</v>
@@ -9837,15 +9909,15 @@
       <c r="J79" s="5" t="n">
         <v>2889.57</v>
       </c>
-      <c r="K79" s="6" t="n">
-        <v>-54.52</v>
+      <c r="K79" s="7" t="n">
+        <v>34674.72</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>217278.57</v>
+        <v>248793.75</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9865,14 +9937,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>8</v>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>7.025</v>
       </c>
       <c r="G80" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.025</v>
+        <v>6.975</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>204993.06</v>
@@ -9880,15 +9960,15 @@
       <c r="J80" s="5" t="n">
         <v>2849.4</v>
       </c>
-      <c r="K80" s="6" t="n">
-        <v>-71.23999999999999</v>
+      <c r="K80" s="7" t="n">
+        <v>19874.59</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>217207.33</v>
+        <v>268668.34</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9927,7 +10007,7 @@
         <v>-35.12</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>213958.15</v>
+        <v>268616.43</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9978,11 +10058,183 @@
         <v>-3214.06</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>213993.27</v>
+        <v>214119.03</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>205570.26</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>2857.43</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>268652.14</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>202712.83</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>2817.71</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>268662.06</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>199895.12</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>2778.54</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>268651.56</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>257404.86</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>3577.93</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>268662.22</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose8_portfolio_daily.xlsx
+++ b/output/quickfixclose8_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>218,367.58</t>
+          <t>260,140.10</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+118.37%</t>
+          <t>+160.14%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>226,032  (+126.03%)</t>
+          <t>269,218  (+169.22%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,985  (7.7 pts of return)</t>
+          <t>4,032  (9.1 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.4x</t>
+          <t>8.7x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+7.30R  (best +27.82R)</t>
+          <t>+8.00R  (best +27.82R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,911  (+7.30%)</t>
+          <t>9,350  (+8.00%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,276  (-1.28%)</t>
+          <t>-1,291  (-1.28%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>80% of trading days</t>
+          <t>81% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5823,26 +5823,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>218367.58</v>
+        <v>218399.98</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>9195.809999999999</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>209204.16</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,113)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>260140.1</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>218367.58</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>260140.1</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 2,113)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,092); NY_Palladium_Futures short (risk 2,071)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-2,128); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_close (+43,888)</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9988,14 +10016,22 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>8</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>24.85</v>
       </c>
       <c r="G81" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.013</v>
+        <v>24.825</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>202143.66</v>
@@ -10003,15 +10039,15 @@
       <c r="J81" s="5" t="n">
         <v>2809.8</v>
       </c>
-      <c r="K81" s="6" t="n">
-        <v>-35.12</v>
+      <c r="K81" s="7" t="n">
+        <v>69753.21000000001</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>268616.43</v>
+        <v>334785.31</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10137,7 @@
         <v>-9.92</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>268652.14</v>
+        <v>265032.69</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10144,7 +10180,7 @@
         <v>-0.16</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>268662.06</v>
+        <v>265065.79</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10187,7 +10223,7 @@
         <v>-0.59</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>268651.56</v>
+        <v>265032.1</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -10211,14 +10247,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>257404.86</v>
@@ -10227,12 +10271,98 @@
         <v>3577.93</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>-6.12</v>
+        <v>-3602.39</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>268662.22</v>
+        <v>265065.94</v>
       </c>
       <c r="M86" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>253826.93</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>3528.19</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>265056.25</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>250298.74</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>3479.15</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>265042.61</v>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
